--- a/dev/review_manual/Excel_test.xlsx
+++ b/dev/review_manual/Excel_test.xlsx
@@ -869,17 +869,17 @@
       </c>
       <c r="C3" s="34" t="inlineStr">
         <is>
-          <t>1-Democrat</t>
+          <t>Democrat</t>
         </is>
       </c>
       <c r="D3" s="33" t="inlineStr">
         <is>
-          <t>2-Independent, other</t>
+          <t>Independent, other</t>
         </is>
       </c>
       <c r="E3" s="33" t="inlineStr">
         <is>
-          <t>3-Republican</t>
+          <t>Republican</t>
         </is>
       </c>
       <c r="F3" s="34" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>1-Lt $10000</t>
+          <t>Lt $10000</t>
         </is>
       </c>
       <c r="C8" s="50">
@@ -1120,7 +1120,7 @@
       <c r="A9" s="38"/>
       <c r="B9" s="37" t="inlineStr">
         <is>
-          <t>2-$10000 to 14999</t>
+          <t>$10000 to 14999</t>
         </is>
       </c>
       <c r="C9" s="50">
@@ -1158,7 +1158,7 @@
       <c r="A10" s="38"/>
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>3-$15000 to 24999</t>
+          <t>$15000 to 24999</t>
         </is>
       </c>
       <c r="C10" s="50">
@@ -1196,7 +1196,7 @@
       <c r="A11" s="38"/>
       <c r="B11" s="37" t="inlineStr">
         <is>
-          <t>4-$25000 or more</t>
+          <t>$25000 or more</t>
         </is>
       </c>
       <c r="C11" s="50">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B13" s="37" t="inlineStr">
         <is>
-          <t>1-Protestant</t>
+          <t>Protestant</t>
         </is>
       </c>
       <c r="C13" s="50">
@@ -1314,7 +1314,7 @@
       <c r="A14" s="38"/>
       <c r="B14" s="37" t="inlineStr">
         <is>
-          <t>2-Catholic</t>
+          <t>Catholic</t>
         </is>
       </c>
       <c r="C14" s="50">
@@ -1352,7 +1352,7 @@
       <c r="A15" s="38"/>
       <c r="B15" s="37" t="inlineStr">
         <is>
-          <t>3-Other christian</t>
+          <t>Other christian</t>
         </is>
       </c>
       <c r="C15" s="50">
@@ -1390,7 +1390,7 @@
       <c r="A16" s="38"/>
       <c r="B16" s="37" t="inlineStr">
         <is>
-          <t>4-Jewish</t>
+          <t>Jewish</t>
         </is>
       </c>
       <c r="C16" s="52">
@@ -1428,7 +1428,7 @@
       <c r="A17" s="38"/>
       <c r="B17" s="37" t="inlineStr">
         <is>
-          <t>5-Buddhist/Hinduist</t>
+          <t>Buddhist/Hinduist</t>
         </is>
       </c>
       <c r="C17" s="53">
@@ -1466,7 +1466,7 @@
       <c r="A18" s="38"/>
       <c r="B18" s="37" t="inlineStr">
         <is>
-          <t>6-Muslim</t>
+          <t>Muslim</t>
         </is>
       </c>
       <c r="C18" s="52">
@@ -1504,7 +1504,7 @@
       <c r="A19" s="38"/>
       <c r="B19" s="37" t="inlineStr">
         <is>
-          <t>7-Other</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" s="50">
@@ -1542,7 +1542,7 @@
       <c r="A20" s="38"/>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>8-None</t>
+          <t>None</t>
         </is>
       </c>
       <c r="C20" s="50">
@@ -1789,7 +1789,6 @@
           </r>
           <r>
             <rPr>
-              <b/>
               <sz val="9"/>
               <color rgb="FF6492B0"/>
               <rFont val="DejaVu Sans Condensed"/>
@@ -1805,7 +1804,6 @@
           </r>
           <r>
             <rPr>
-              <b/>
               <sz val="9"/>
               <color rgb="FF5E85B8"/>
               <rFont val="DejaVu Sans Condensed"/>
@@ -1821,7 +1819,6 @@
           </r>
           <r>
             <rPr>
-              <b/>
               <sz val="9"/>
               <color rgb="FF5169C7"/>
               <rFont val="DejaVu Sans Condensed"/>
@@ -1851,7 +1848,6 @@
           </r>
           <r>
             <rPr>
-              <b/>
               <sz val="9"/>
               <color rgb="FFAE815E"/>
               <rFont val="DejaVu Sans Condensed"/>
@@ -1867,7 +1863,6 @@
           </r>
           <r>
             <rPr>
-              <b/>
               <sz val="9"/>
               <color rgb="FFB56E53"/>
               <rFont val="DejaVu Sans Condensed"/>
@@ -1883,7 +1878,6 @@
           </r>
           <r>
             <rPr>
-              <b/>
               <sz val="9"/>
               <color rgb="FFBE4034"/>
               <rFont val="DejaVu Sans Condensed"/>
